--- a/credenciais.xlsx
+++ b/credenciais.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Usuario</t>
   </si>
@@ -38,7 +38,10 @@
     <t>fs27106</t>
   </si>
   <si>
-    <t>teste</t>
+    <t>0361198680</t>
+  </si>
+  <si>
+    <t>fabioconne</t>
   </si>
 </sst>
 </file>
@@ -654,8 +657,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1191,10 +1200,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="9.57142857142857"/>
+    <col min="1" max="1" width="31.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="9.66666666666667"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1214,11 +1224,19 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
+      <c r="B3">
+        <v>32458758</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>32458758</v>
       </c>
     </row>
   </sheetData>
